--- a/originales/respuestas/2025/01. Calificadas/root/Secretaría Distrital De Integración Social.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/root/Secretaría Distrital De Integración Social.xlsx
@@ -439,7 +439,7 @@
     <t>¿Su entidad ha puesto a disposición de todos formación orientada al fortalecimiento de capacidades en innovación?</t>
   </si>
   <si>
-    <t>Pregunta 30</t>
+    <t>Pregunta 30.</t>
   </si>
   <si>
     <t>¿Qué estrategias o iniciativas ha implementado su entidad para fomentar una cultura de innovación entre sus funcionarios y contratistas?</t>
@@ -448,7 +448,7 @@
     <t>Programas de sensibilización sobre innovación pública., Espacios de ideación y cocreación con los equipos internos., Incentivos o reconocimientos a iniciativas innovadoras de los funcionarios., Procesos de formación o capacitaciones en metodologías de innovación., Creación de equipos o laboratorios de innovación internos., Otras (Alianzas con otros actores del ecosistema de innovación: Bloomberg, IBO y otras entidades).</t>
   </si>
   <si>
-    <t>Pregunta 31</t>
+    <t>Pregunta 31.</t>
   </si>
   <si>
     <t>¿De qué manera ha incentivado su entidad la participación de los funcionarios y contratistas en procesos de innovación?</t>
@@ -4963,7 +4963,9 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="31" width="10.71"/>
+    <col customWidth="1" min="1" max="6" width="10.71"/>
+    <col customWidth="1" min="7" max="7" width="28.0"/>
+    <col customWidth="1" min="8" max="31" width="10.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="43.5" customHeight="1">
@@ -5815,7 +5817,7 @@
       <c r="C18" s="7">
         <v>17.0</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="8" t="s">
         <v>133</v>
       </c>
       <c r="E18" s="6"/>
@@ -5858,7 +5860,7 @@
       <c r="C19" s="11">
         <v>18.0</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="12" t="s">
         <v>136</v>
       </c>
       <c r="E19" s="10"/>
@@ -6936,7 +6938,11 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="31" width="10.71"/>
+    <col customWidth="1" min="1" max="6" width="10.71"/>
+    <col customWidth="1" min="7" max="7" width="22.0"/>
+    <col customWidth="1" min="8" max="8" width="10.71"/>
+    <col customWidth="1" min="9" max="9" width="25.71"/>
+    <col customWidth="1" min="10" max="31" width="10.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="43.5" customHeight="1">
